--- a/data/trans_dic/P64D$otros_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P64D$otros_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,2</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,4</t>
+          <t>0,62; 5,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 5,75</t>
+          <t>0,39; 6,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,41</t>
+          <t>0,88; 4,23</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,2</t>
+          <t>0,63; 5,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,82</t>
+          <t>0,32; 2,82</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 7,3</t>
+          <t>0,55; 6,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,09</t>
+          <t>0,33; 4,04</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,84</t>
+          <t>0,33; 2,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,96</t>
+          <t>0,74; 3,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,67</t>
+          <t>0,72; 2,53</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,3</t>
+          <t>0,0; 0,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,75</t>
+          <t>0,01; 0,77</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,4</t>
+          <t>0,42; 1,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,16</t>
+          <t>0,31; 1,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,1</t>
+          <t>0,49; 1,11</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4228</t>
+          <t>0; 3654</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1074</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4013</t>
+          <t>0; 3973</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1511; 13272</t>
+          <t>1512; 13049</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>632; 9525</t>
+          <t>648; 10259</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3231; 18151</t>
+          <t>3618; 17384</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>906; 7728</t>
+          <t>939; 8072</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1364</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>888; 7597</t>
+          <t>876; 7612</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2547</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2434</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2486</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1274</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 853</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1031</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>770; 9859</t>
+          <t>744; 8778</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1274</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>741; 9068</t>
+          <t>732; 8946</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>957; 9507</t>
+          <t>1094; 9264</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2190; 12151</t>
+          <t>2256; 11802</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4477; 17126</t>
+          <t>4613; 16224</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 8029</t>
+          <t>0; 6180</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 814</t>
+          <t>0; 766</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>126; 6746</t>
+          <t>127; 6954</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>8230; 27537</t>
+          <t>8286; 27774</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4348; 16983</t>
+          <t>4559; 16711</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15689; 37855</t>
+          <t>16684; 38207</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$otros_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P64D$otros_2023-Provincia-trans_dic.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,31</t>
+          <t>0,59; 5,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 6,19</t>
+          <t>0,37; 5,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,23</t>
+          <t>0,92; 4,47</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,43</t>
+          <t>0,59; 6,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,82</t>
+          <t>0,33; 3,25</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,5</t>
+          <t>0,54; 6,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,04</t>
+          <t>0,32; 3,74</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,77</t>
+          <t>0,3; 2,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,85</t>
+          <t>1,0; 4,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,53</t>
+          <t>0,94; 3,14</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,28</t>
+          <t>0,0; 2,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,77</t>
+          <t>0,17; 1,53</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,41</t>
+          <t>0,7; 1,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,14</t>
+          <t>0,47; 1,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,11</t>
+          <t>0,67; 1,42</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>1579</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3654</t>
+          <t>0; 5628</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3973</t>
+          <t>0; 4829</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>9386</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1512; 13049</t>
+          <t>1494; 15085</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>648; 10259</t>
+          <t>642; 10270</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3618; 17384</t>
+          <t>3936; 19116</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3532</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>939; 8072</t>
+          <t>878; 9094</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>876; 7612</t>
+          <t>901; 8863</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3019</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>744; 8778</t>
+          <t>741; 8475</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>732; 8946</t>
+          <t>720; 8353</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>12934</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1094; 9264</t>
+          <t>1159; 10770</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2256; 11802</t>
+          <t>3634; 17355</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4613; 16224</t>
+          <t>7032; 23528</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>3933</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 6180</t>
+          <t>0; 8819</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 766</t>
+          <t>0; 8681</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>127; 6954</t>
+          <t>1292; 11725</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25791</t>
+          <t>34384</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>8286; 27774</t>
+          <t>13532; 33169</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4559; 16711</t>
+          <t>7113; 24994</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16684; 38207</t>
+          <t>23200; 48742</t>
         </is>
       </c>
     </row>
